--- a/feedback_surveys/009_fun_group_dynamics_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/009_fun_group_dynamics_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>very good</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>very_fair</t>
+          <t>very fair</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>very_funny</t>
+          <t>very funny</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>somewhat_funny</t>
+          <t>somewhat funny</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>not_fun</t>
+          <t>not fun</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>positive_and_negative</t>
+          <t>positive and negative</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>very_negative</t>
+          <t>very negative</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>by_random</t>
+          <t>by random</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>by_skill</t>
+          <t>by skill</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>by_interest</t>
+          <t>by interest</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>very_open</t>
+          <t>very open</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>somewhat_open</t>
+          <t>somewhat open</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>not_open</t>
+          <t>not open</t>
         </is>
       </c>
     </row>
